--- a/artfynd/A 6850-2024 artfynd.xlsx
+++ b/artfynd/A 6850-2024 artfynd.xlsx
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Forsman, Catharina Forsman</t>
+          <t>Catharina Forsman, Mikael Forsman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 6850-2024 artfynd.xlsx
+++ b/artfynd/A 6850-2024 artfynd.xlsx
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Catharina Forsman, Mikael Forsman</t>
+          <t>Mikael Forsman, Catharina Forsman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
